--- a/src/proyecto/prospeccion/contactos-campana-octubre-2026.xlsx
+++ b/src/proyecto/prospeccion/contactos-campana-octubre-2026.xlsx
@@ -7675,7 +7675,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Organismos: frase que completa «Could you help us …?». Universidades: el [ÁREA] del correo 3. Empresas: tema para preparar la visita (el correo no lo usa).</t>
+          <t>Tema para preparar la visita o la llamada. Los correos son genéricos y no lo usan; en las universidades es el [ÁREA] del correo 3.</t>
         </is>
       </c>
     </row>
